--- a/data/ICICI _ELEVATE _PLAN.xlsx
+++ b/data/ICICI _ELEVATE _PLAN.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="88">
   <si>
     <t>TC_ID</t>
   </si>
@@ -123,9 +123,9 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
       </rPr>
       <t>test@gmail.com</t>
     </r>
@@ -149,32 +149,12 @@
     <t>SPOUSE</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_03</t>
   </si>
   <si>
     <t>MOTHER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -184,354 +164,143 @@
     <t>FATHER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_05</t>
   </si>
   <si>
     <t>SON</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_06</t>
   </si>
   <si>
     <t>DAUGHTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_07</t>
   </si>
   <si>
     <t>SELF+1SON</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_08</t>
   </si>
   <si>
     <t>SELF+1SON+1DAUGHTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_09</t>
   </si>
   <si>
     <t>SPOUSE+1SON+2DAUGHTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_10</t>
   </si>
   <si>
     <t>FATHER+MOTHER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_11</t>
   </si>
   <si>
     <t>SELF+SPOUSE</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_12</t>
   </si>
   <si>
     <t>SELF+FATHER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_13</t>
   </si>
   <si>
     <t>SELF+MOTHER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_14</t>
   </si>
   <si>
     <t>SPOUSE+FATHER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_15</t>
   </si>
   <si>
     <t>SPOUSE+MOTHER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_16</t>
   </si>
   <si>
     <t>SELF+SPOUSE+1SON</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_17</t>
   </si>
   <si>
     <t>SELF+SPOUSE+2SON+1DAUGHTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_18</t>
   </si>
   <si>
     <t>SELF+SPOUSE+1SON+1DAUGHTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_19</t>
   </si>
   <si>
     <t>SELF+FATHER+1SON</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_20</t>
   </si>
   <si>
     <t>SPOUSE+MOTHER+1SON+1DAUGHTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_21</t>
   </si>
   <si>
     <t>FATHER+SON</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_22</t>
   </si>
   <si>
     <t>MOTHER+DAUGHTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_23</t>
   </si>
   <si>
     <t>FATHER+MOTHER+1SON+1DAUGHTER</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
-  </si>
-  <si>
     <t>TC_24</t>
   </si>
   <si>
     <t>SPOUSE+MOTHER+2SON+1DAUGHTER</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>test@gmail.com</t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -545,101 +314,166 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -651,146 +485,213 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AG90"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="33" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -891,7 +792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
@@ -902,13 +803,13 @@
         <v>35</v>
       </c>
       <c r="D2" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F2" s="4">
-        <v>500000.0</v>
+        <v>500000</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>37</v>
@@ -926,10 +827,10 @@
         <v>40</v>
       </c>
       <c r="L2" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="M2" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -952,7 +853,7 @@
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
@@ -963,13 +864,13 @@
         <v>35</v>
       </c>
       <c r="D3" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F3" s="4">
-        <v>750000.0</v>
+        <v>750000</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>37</v>
@@ -987,10 +888,10 @@
         <v>40</v>
       </c>
       <c r="L3" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="M3" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -1013,24 +914,24 @@
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4">
-        <v>1000000.0</v>
+        <v>1000000</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>37</v>
@@ -1042,16 +943,16 @@
         <v>39</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="L4" s="4">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="M4" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -1074,24 +975,24 @@
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4">
-        <v>1500000.0</v>
+        <v>1500000</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>37</v>
@@ -1103,16 +1004,16 @@
         <v>39</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L5" s="4">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="M5" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -1135,24 +1036,24 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D6" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F6" s="4">
-        <v>2000000.0</v>
+        <v>2000000</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>37</v>
@@ -1164,16 +1065,16 @@
         <v>39</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L6" s="4">
-        <v>6.0</v>
+        <v>29</v>
       </c>
       <c r="M6" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1196,24 +1097,24 @@
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F7" s="4">
-        <v>2500000.0</v>
+        <v>2500000</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>37</v>
@@ -1225,16 +1126,16 @@
         <v>39</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L7" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="M7" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -1257,24 +1158,24 @@
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="F8" s="4">
-        <v>500000.0</v>
+        <v>500000</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>37</v>
@@ -1292,22 +1193,22 @@
         <v>40</v>
       </c>
       <c r="L8" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="M8" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P8" s="4">
-        <v>2.0</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -1326,24 +1227,24 @@
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D9" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="F9" s="4">
-        <v>1000000.0</v>
+        <v>1000000</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>37</v>
@@ -1358,37 +1259,37 @@
         <v>34</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L9" s="4">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="M9" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P9" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="T9" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="U9" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1403,24 +1304,24 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="F10" s="4">
-        <v>1000000.0</v>
+        <v>1000000</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>37</v>
@@ -1435,49 +1336,49 @@
         <v>42</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L10" s="4">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="M10" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P10" s="4">
-        <v>10.0</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="T10" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="U10" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="X10" s="4">
-        <v>30.0</v>
+        <v>8</v>
       </c>
       <c r="Y10" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
@@ -1488,24 +1389,24 @@
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D11" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="F11" s="4">
-        <v>1000000.0</v>
+        <v>1000000</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>37</v>
@@ -1517,28 +1418,28 @@
         <v>39</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>40</v>
       </c>
       <c r="L11" s="4">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="M11" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="P11" s="4">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="Q11" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
@@ -1557,24 +1458,24 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F12" s="4">
-        <v>1500000.0</v>
+        <v>1500000</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>37</v>
@@ -1592,22 +1493,22 @@
         <v>40</v>
       </c>
       <c r="L12" s="4">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="M12" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P12" s="4">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="Q12" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
@@ -1626,24 +1527,24 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D13" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="F13" s="4">
-        <v>2000000.0</v>
+        <v>2000000</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>37</v>
@@ -1661,22 +1562,22 @@
         <v>40</v>
       </c>
       <c r="L13" s="4">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="M13" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P13" s="4">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
@@ -1695,24 +1596,24 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="F14" s="4">
-        <v>2500000.0</v>
+        <v>2500000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>37</v>
@@ -1730,22 +1631,22 @@
         <v>40</v>
       </c>
       <c r="L14" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="M14" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="P14" s="4">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="Q14" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
@@ -1764,24 +1665,24 @@
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="F15" s="4">
-        <v>5000000.0</v>
+        <v>5000000</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>37</v>
@@ -1796,25 +1697,25 @@
         <v>42</v>
       </c>
       <c r="K15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" s="4">
+        <v>24</v>
+      </c>
+      <c r="M15" s="4">
+        <v>421305</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L15" s="4">
-        <v>24.0</v>
-      </c>
-      <c r="M15" s="4">
-        <v>421305.0</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="4">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="Q15" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
@@ -1833,24 +1734,24 @@
       <c r="AF15" s="3"/>
       <c r="AG15" s="3"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D16" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="F16" s="4">
-        <v>500000.0</v>
+        <v>500000</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>37</v>
@@ -1868,22 +1769,22 @@
         <v>40</v>
       </c>
       <c r="L16" s="4">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="M16" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="P16" s="4">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
@@ -1902,24 +1803,24 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="F17" s="4">
-        <v>1000000.0</v>
+        <v>1000000</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>37</v>
@@ -1937,34 +1838,34 @@
         <v>40</v>
       </c>
       <c r="L17" s="4">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="M17" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P17" s="4">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="Q17" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>40</v>
       </c>
       <c r="T17" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="U17" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -1979,24 +1880,24 @@
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="F18" s="4">
-        <v>1000000.0</v>
+        <v>1000000</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>37</v>
@@ -2014,82 +1915,82 @@
         <v>40</v>
       </c>
       <c r="L18" s="4">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="M18" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>42</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P18" s="4">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="Q18" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="T18" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="U18" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="X18" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="Y18" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="Z18" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AB18" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="AC18" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D19" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="F19" s="4">
-        <v>1500000.0</v>
+        <v>1500000</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>37</v>
@@ -2107,46 +2008,46 @@
         <v>40</v>
       </c>
       <c r="L19" s="4">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="M19" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>42</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P19" s="4">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="Q19" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>40</v>
       </c>
       <c r="T19" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="U19" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="X19" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="Y19" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
@@ -2157,24 +2058,24 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="F20" s="4">
-        <v>2000000.0</v>
+        <v>2000000</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>37</v>
@@ -2192,34 +2093,34 @@
         <v>40</v>
       </c>
       <c r="L20" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="M20" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="4">
+        <v>46</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>421305</v>
+      </c>
+      <c r="R20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P20" s="4">
-        <v>46.0</v>
-      </c>
-      <c r="Q20" s="4">
-        <v>421305.0</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="T20" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="U20" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2234,24 +2135,24 @@
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D21" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="F21" s="4">
-        <v>500000.0</v>
+        <v>500000</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>37</v>
@@ -2269,46 +2170,46 @@
         <v>40</v>
       </c>
       <c r="L21" s="4">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="M21" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="P21" s="4">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="Q21" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="T21" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="U21" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>40</v>
       </c>
       <c r="X21" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="Y21" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
@@ -2319,24 +2220,24 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="F22" s="4">
-        <v>1000000.0</v>
+        <v>1000000</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>37</v>
@@ -2348,28 +2249,28 @@
         <v>39</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L22" s="4">
+        <v>40</v>
+      </c>
+      <c r="M22" s="4">
+        <v>421305</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L22" s="4">
-        <v>40.0</v>
-      </c>
-      <c r="M22" s="4">
-        <v>421305.0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>40</v>
       </c>
       <c r="P22" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -2388,24 +2289,24 @@
       <c r="AF22" s="3"/>
       <c r="AG22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D23" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="F23" s="4">
-        <v>1000000.0</v>
+        <v>1000000</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>37</v>
@@ -2417,28 +2318,28 @@
         <v>39</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="L23" s="4">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="M23" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P23" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="Q23" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -2457,24 +2358,24 @@
       <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D24" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="F24" s="4">
-        <v>1500000.0</v>
+        <v>1500000</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>37</v>
@@ -2486,52 +2387,52 @@
         <v>39</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L24" s="4">
+        <v>50</v>
+      </c>
+      <c r="M24" s="4">
+        <v>421305</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P24" s="4">
+        <v>48</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>421305</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T24" s="4">
+        <v>5</v>
+      </c>
+      <c r="U24" s="4">
+        <v>421305</v>
+      </c>
+      <c r="V24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L24" s="4">
-        <v>50.0</v>
-      </c>
-      <c r="M24" s="4">
-        <v>421305.0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P24" s="4">
-        <v>48.0</v>
-      </c>
-      <c r="Q24" s="4">
-        <v>421305.0</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="T24" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="U24" s="4">
-        <v>421305.0</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="X24" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="Y24" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
@@ -2542,24 +2443,24 @@
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="4">
-        <v>9.111111111E9</v>
+        <v>9111111111</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="F25" s="4">
-        <v>2000000.0</v>
+        <v>2000000</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>37</v>
@@ -2577,286 +2478,287 @@
         <v>40</v>
       </c>
       <c r="L25" s="4">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="M25" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O25" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="P25" s="4">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="Q25" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>40</v>
       </c>
       <c r="T25" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="U25" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="W25" s="3" t="s">
         <v>40</v>
       </c>
       <c r="X25" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="Y25" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="Z25" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AB25" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="AC25" s="4">
-        <v>421305.0</v>
+        <v>421305</v>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
       <c r="AG25" s="3"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E2"/>
-    <hyperlink r:id="rId2" ref="E3"/>
-    <hyperlink r:id="rId3" ref="E4"/>
-    <hyperlink r:id="rId4" ref="E5"/>
-    <hyperlink r:id="rId5" ref="E6"/>
-    <hyperlink r:id="rId6" ref="E7"/>
-    <hyperlink r:id="rId7" ref="E8"/>
-    <hyperlink r:id="rId8" ref="E9"/>
-    <hyperlink r:id="rId9" ref="E10"/>
-    <hyperlink r:id="rId10" ref="E11"/>
-    <hyperlink r:id="rId11" ref="E12"/>
-    <hyperlink r:id="rId12" ref="E13"/>
-    <hyperlink r:id="rId13" ref="E14"/>
-    <hyperlink r:id="rId14" ref="E15"/>
-    <hyperlink r:id="rId15" ref="E16"/>
-    <hyperlink r:id="rId16" ref="E17"/>
-    <hyperlink r:id="rId17" ref="E18"/>
-    <hyperlink r:id="rId18" ref="E19"/>
-    <hyperlink r:id="rId19" ref="E20"/>
-    <hyperlink r:id="rId20" ref="E21"/>
-    <hyperlink r:id="rId21" ref="E22"/>
-    <hyperlink r:id="rId22" ref="E23"/>
-    <hyperlink r:id="rId23" ref="E24"/>
-    <hyperlink r:id="rId24" ref="E25"/>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
   </hyperlinks>
-  <drawing r:id="rId25"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/ICICI _ELEVATE _PLAN.xlsx
+++ b/data/ICICI _ELEVATE _PLAN.xlsx
@@ -313,13 +313,13 @@
     <t>TC_28</t>
   </si>
   <si>
-    <t>Infinite Care, Room Modifier, Convalescence Benefit, Annual Health Checkup, Voluntary CoPay, Network Advantage, Befit, Inflation Protector, Claim Protector, Nursing at Home, Dependent Accomodation, Durable Medical Equipment Cover, Domestic Air Ambulance Cover, Critical Illness, Compassionate Visit, Guaranteed Super Bonus, Two Hour Hospitalisation, Worldwide, Tele Consultation, Personal Accident</t>
+    <t>Infinite Care, Convalescence Benefit, Network Advantage, Inflation Protector, Claim Protector, Nursing at Home, Dependent Accomodation, Domestic Air Ambulance Cover, Compassionate Visit, Guaranteed Super Bonus, Worldwide, Tele Consultation</t>
   </si>
   <si>
     <t>TC_29</t>
   </si>
   <si>
-    <t>Infinite Care, Room Modifier, Convalescence Benefit, Voluntary CoPay, Network Advantage, Befit, Inflation Protector, Claim Protector, Nursing at Home, Dependent Accomodation, Durable Medical Equipment Cover, Domestic Air Ambulance Cover, Critical Illness, Compassionate Visit, Guaranteed Super Bonus, Two Hour Hospitalisation, Worldwide, Tele Consultation, Personal Accident</t>
+    <t>Infinite Care, Convalescence Benefit, Network Advantage, Inflation Protector,  Compassionate Visit, Guaranteed Super Bonus, Worldwide, Tele Consultation</t>
   </si>
 </sst>
 </file>
